--- a/Data/5odam.xlsx
+++ b/Data/5odam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\marmina\api\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\marmina\api\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCDA0E2-EEF5-4A1C-B265-0DAAE99631AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D839FB53-D22C-4761-924B-57AE5D2B1D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -913,9 +913,6 @@
     <t>امين اسرة</t>
   </si>
   <si>
-    <t>امين مساعد</t>
-  </si>
-  <si>
     <t>امين مرحلة</t>
   </si>
   <si>
@@ -1010,6 +1007,9 @@
   </si>
   <si>
     <t>ابونا بموا</t>
+  </si>
+  <si>
+    <t>.امين مساعد اسرة</t>
   </si>
 </sst>
 </file>
@@ -1564,28 +1564,28 @@
         <v>0</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="R1" s="6" t="s">
         <v>289</v>
@@ -1638,13 +1638,13 @@
         <v>292</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1691,16 +1691,16 @@
         <v>9</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1747,16 +1747,16 @@
         <v>13</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,13 +1806,13 @@
         <v>292</v>
       </c>
       <c r="O5" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q5" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1859,16 +1859,16 @@
         <v>21</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1912,19 +1912,19 @@
         <v>2023</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1974,13 +1974,13 @@
         <v>292</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2030,13 +2030,13 @@
         <v>292</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2083,16 +2083,16 @@
         <v>37</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2139,16 +2139,16 @@
         <v>41</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P11" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q11" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2192,17 +2192,17 @@
         <v>2020</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2249,16 +2249,16 @@
         <v>48</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P13" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q13" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2305,16 +2305,16 @@
         <v>53</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P14" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q14" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2361,14 +2361,14 @@
         <v>57</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2412,19 +2412,19 @@
         <v>61</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q16" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2471,16 +2471,16 @@
         <v>65</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2527,16 +2527,16 @@
         <v>69</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,13 +2586,13 @@
         <v>292</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2639,16 +2639,16 @@
         <v>37</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P20" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q20" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2695,16 +2695,16 @@
         <v>81</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2751,16 +2751,16 @@
         <v>41</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2807,16 +2807,16 @@
         <v>17</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2863,16 +2863,16 @@
         <v>53</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2919,16 +2919,16 @@
         <v>96</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P25" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2975,16 +2975,16 @@
         <v>100</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P26" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3031,10 +3031,10 @@
         <v>41</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
@@ -3083,16 +3083,16 @@
         <v>108</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3142,13 +3142,13 @@
         <v>292</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3251,16 +3251,16 @@
         <v>120</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>65</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
@@ -3356,19 +3356,19 @@
         <v>129</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>292</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3415,16 +3415,16 @@
         <v>133</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O34" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P34" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q34" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3471,16 +3471,16 @@
         <v>138</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O35" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P35" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P35" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q35" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3527,16 +3527,16 @@
         <v>142</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3583,16 +3583,16 @@
         <v>48</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3639,16 +3639,16 @@
         <v>138</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3695,16 +3695,16 @@
         <v>138</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O39" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P39" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q39" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3751,16 +3751,16 @@
         <v>21</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R40" s="12"/>
     </row>
@@ -3808,14 +3808,14 @@
         <v>160</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P41" s="4"/>
       <c r="Q41" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3862,16 +3862,16 @@
         <v>164</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P42" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3918,16 +3918,16 @@
         <v>108</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R43" s="12"/>
     </row>
@@ -3975,16 +3975,16 @@
         <v>138</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4031,16 +4031,16 @@
         <v>133</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4087,16 +4087,16 @@
         <v>177</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,16 +4143,16 @@
         <v>181</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O47" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="P47" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="Q47" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4199,16 +4199,16 @@
         <v>9</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4255,16 +4255,16 @@
         <v>164</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4311,16 +4311,16 @@
         <v>133</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4367,16 +4367,16 @@
         <v>48</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4423,16 +4423,16 @@
         <v>164</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4479,16 +4479,16 @@
         <v>48</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4535,16 +4535,16 @@
         <v>207</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4591,16 +4591,16 @@
         <v>17</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4647,16 +4647,16 @@
         <v>214</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4703,16 +4703,16 @@
         <v>164</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4759,16 +4759,16 @@
         <v>221</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4815,16 +4815,16 @@
         <v>226</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q59" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4871,16 +4871,16 @@
         <v>230</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q60" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4930,13 +4930,13 @@
         <v>292</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4983,16 +4983,16 @@
         <v>164</v>
       </c>
       <c r="N62" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q62" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5039,16 +5039,16 @@
         <v>243</v>
       </c>
       <c r="N63" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5095,16 +5095,16 @@
         <v>247</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5151,16 +5151,16 @@
         <v>164</v>
       </c>
       <c r="N65" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q65" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5207,16 +5207,16 @@
         <v>138</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q66" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5263,16 +5263,16 @@
         <v>160</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q67" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5319,16 +5319,16 @@
         <v>261</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5375,16 +5375,16 @@
         <v>48</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q69" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5431,16 +5431,16 @@
         <v>112</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q70" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5487,16 +5487,16 @@
         <v>138</v>
       </c>
       <c r="N71" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q71" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5543,16 +5543,16 @@
         <v>17</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5599,16 +5599,16 @@
         <v>279</v>
       </c>
       <c r="N73" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q73" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5655,16 +5655,16 @@
         <v>48</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q74" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
